--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260818.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260818.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>134,285</t>
+          <t>130,785</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>27.48%</t>
+          <t>27.44%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>15,325</t>
+          <t>14,925</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.62%</t>
+          <t>8.27%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>97,430</t>
+          <t>94,830</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.45%</t>
+          <t>7.47%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>49,615</t>
+          <t>48,315</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.06%</t>
+          <t>5.76%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>118,395</t>
+          <t>115,295</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.32%</t>
+          <t>5.49%</t>
         </is>
       </c>
     </row>
@@ -721,78 +721,78 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>58,240</t>
+          <t>56,740</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.74%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>5,585</t>
+          <t>189,186,882</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.27%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>64,005</t>
+          <t>5,435</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.25%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>17,853</t>
+          <t>62,305</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
@@ -809,78 +809,78 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>44,115</t>
+          <t>42,915</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>19,285</t>
+          <t>17,353</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.89%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>75,045</t>
+          <t>18,785</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>19,845</t>
+          <t>73,045</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
@@ -897,100 +897,100 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>30,770</t>
+          <t>29,970</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>119,481,380</t>
+          <t>19,345</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>3,560,612</t>
+          <t>48,645</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>49,945</t>
+          <t>11,151</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>11,451</t>
+          <t>34,430</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -1007,78 +1007,78 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>25,928</t>
+          <t>25,228</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>35,430</t>
+          <t>18,490</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>18,990</t>
+          <t>56,508</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>58,008</t>
+          <t>7,590</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1095,78 +1095,78 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>9,336</t>
+          <t>9,136</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>7,790</t>
+          <t>20,298</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>20,848</t>
+          <t>120,885</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>124,185</t>
+          <t>17,525</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -1183,100 +1183,100 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>19,137</t>
+          <t>18,637</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>18,025</t>
+          <t>15,071</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>15,471</t>
+          <t>41,210</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>42,310</t>
+          <t>35,730</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>36,730</t>
+          <t>1,359,494</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>11,515</t>
+          <t>11,215</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>96,005,000</t>
+          <t>175,637,500</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>298,882</t>
+          <t>4,832,346</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
